--- a/output/laminas_comunales/comunal_o_ocup_a_2023_los_lagos.xlsx
+++ b/output/laminas_comunales/comunal_o_ocup_a_2023_los_lagos.xlsx
@@ -352,7 +352,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:C31"/>
+  <dimension ref="A1:C232"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -384,7 +384,7 @@
         </is>
       </c>
       <c r="C2">
-        <v>42.605796329583</v>
+        <v>60.7344283741551</v>
       </c>
     </row>
     <row r="3">
@@ -399,262 +399,262 @@
         </is>
       </c>
       <c r="C3">
-        <v>41.7879591538413</v>
+        <v>59.4851521658966</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>10208</t>
+          <t>10107</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Quellón</t>
+          <t>Llanquihue</t>
         </is>
       </c>
       <c r="C4">
-        <v>40.3755868544601</v>
+        <v>59.2347396768402</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>10107</t>
+          <t>10301</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Llanquihue</t>
+          <t>Osorno</t>
         </is>
       </c>
       <c r="C5">
-        <v>39.9711124167646</v>
+        <v>58.6038630834696</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>10201</t>
+          <t>10107</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Castro</t>
+          <t>Llanquihue</t>
         </is>
       </c>
       <c r="C6">
-        <v>39.4864019360456</v>
+        <v>58.1844933507759</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>10301</t>
+          <t>10201</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Osorno</t>
+          <t>Castro</t>
         </is>
       </c>
       <c r="C7">
-        <v>37.7755037961187</v>
+        <v>57.9937789674573</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>10105</t>
+          <t>10208</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Frutillar</t>
+          <t>Quellón</t>
         </is>
       </c>
       <c r="C8">
-        <v>36.6877582644628</v>
+        <v>57.4864376130199</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>10203</t>
+          <t>10204</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Chonchi</t>
+          <t>Curaco de Vélez</t>
         </is>
       </c>
       <c r="C9">
-        <v>36.6537984282366</v>
+        <v>57.1274509803922</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>10302</t>
+          <t>10301</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Puerto Octay</t>
+          <t>Osorno</t>
         </is>
       </c>
       <c r="C10">
-        <v>35.1250762660159</v>
+        <v>56.5064581956474</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>10205</t>
+          <t>10203</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Dalcahue</t>
+          <t>Chonchi</t>
         </is>
       </c>
       <c r="C11">
-        <v>34.4357169936499</v>
+        <v>55.2622964236026</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>10202</t>
+          <t>10105</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Ancud</t>
+          <t>Frutillar</t>
         </is>
       </c>
       <c r="C12">
-        <v>34.009577028319</v>
+        <v>55.206257172193</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>10307</t>
+          <t>10202</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>San Pablo</t>
+          <t>Ancud</t>
         </is>
       </c>
       <c r="C13">
-        <v>33.9868701206529</v>
+        <v>54.7466766992726</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>10304</t>
+          <t>10302</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Puyehue</t>
+          <t>Puerto Octay</t>
         </is>
       </c>
       <c r="C14">
-        <v>33.7195073813847</v>
+        <v>54.3599656357388</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>10305</t>
+          <t>10307</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Río Negro</t>
+          <t>San Pablo</t>
         </is>
       </c>
       <c r="C15">
-        <v>33.4649713111851</v>
+        <v>54.3592634347989</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>10204</t>
+          <t>10305</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Curaco de Vélez</t>
+          <t>Río Negro</t>
         </is>
       </c>
       <c r="C16">
-        <v>33.4300077339521</v>
+        <v>53.5301953818828</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>10102</t>
+          <t>10303</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Calbuco</t>
+          <t>Purranque</t>
         </is>
       </c>
       <c r="C17">
-        <v>33.1238849416257</v>
+        <v>52.9500694614693</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>10206</t>
+          <t>10102</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Puqueldón</t>
+          <t>Calbuco</t>
         </is>
       </c>
       <c r="C18">
-        <v>32.5166574125486</v>
+        <v>52.6740041928721</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>10303</t>
+          <t>10101</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Purranque</t>
+          <t>Puerto Montt</t>
         </is>
       </c>
       <c r="C19">
-        <v>31.7806395143118</v>
+        <v>52.2376931536469</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>10403</t>
+          <t>10206</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Hualaihué</t>
+          <t>Puqueldón</t>
         </is>
       </c>
       <c r="C20">
-        <v>31.3852592895059</v>
+        <v>52.0151869158879</v>
       </c>
     </row>
     <row r="21">
@@ -669,52 +669,52 @@
         </is>
       </c>
       <c r="C21">
-        <v>31.2481008811911</v>
+        <v>51.7676767676768</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>10209</t>
+          <t>10304</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Quemchi</t>
+          <t>Puyehue</t>
         </is>
       </c>
       <c r="C22">
-        <v>30.5110941734417</v>
+        <v>51.6264798522863</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>10207</t>
+          <t>10109</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Queilén</t>
+          <t>Puerto Varas</t>
         </is>
       </c>
       <c r="C23">
-        <v>30.0845245088441</v>
+        <v>51.4679098005204</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>10401</t>
+          <t>10107</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Chaitén</t>
+          <t>Llanquihue</t>
         </is>
       </c>
       <c r="C24">
-        <v>30.0059382422803</v>
+        <v>51.3051021212838</v>
       </c>
     </row>
     <row r="25">
@@ -729,97 +729,3112 @@
         </is>
       </c>
       <c r="C25">
-        <v>29.7960396945169</v>
+        <v>50.9211531118748</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>10108</t>
+          <t>10209</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Maullín</t>
+          <t>Quemchi</t>
         </is>
       </c>
       <c r="C26">
-        <v>27.2995422153004</v>
+        <v>50.6823384398662</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>10104</t>
+          <t>10205</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Fresia</t>
+          <t>Dalcahue</t>
         </is>
       </c>
       <c r="C27">
-        <v>26.6835901027078</v>
+        <v>50.5986096807415</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>10402</t>
+          <t>10401</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Futaleufú</t>
+          <t>Chaitén</t>
         </is>
       </c>
       <c r="C28">
-        <v>25.4494239777187</v>
+        <v>49.3095238095238</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>10106</t>
+          <t>10207</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Los Muermos</t>
+          <t>Queilén</t>
         </is>
       </c>
       <c r="C29">
-        <v>25.1015297855775</v>
+        <v>49.124162802679</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>10103</t>
+          <t>10201</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Cochamó</t>
+          <t>Castro</t>
         </is>
       </c>
       <c r="C30">
-        <v>20.961266984295</v>
+        <v>48.8540628680134</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
+          <t>10403</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>Hualaihué</t>
+        </is>
+      </c>
+      <c r="C31">
+        <v>48.6935155219945</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>10301</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>Osorno</t>
+        </is>
+      </c>
+      <c r="C32">
+        <v>48.4151667866571</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>10107</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>Llanquihue</t>
+        </is>
+      </c>
+      <c r="C33">
+        <v>48.0258642875525</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>10404</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>Palena</t>
+        </is>
+      </c>
+      <c r="C34">
+        <v>47.7836708453873</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>10101</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>Puerto Montt</t>
+        </is>
+      </c>
+      <c r="C35">
+        <v>47.2523930745984</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>10108</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>Maullín</t>
+        </is>
+      </c>
+      <c r="C36">
+        <v>47.2317797935565</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>10107</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>Llanquihue</t>
+        </is>
+      </c>
+      <c r="C37">
+        <v>46.7031262120859</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>10104</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>Fresia</t>
+        </is>
+      </c>
+      <c r="C38">
+        <v>46.3963066294673</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>10204</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>Curaco de Vélez</t>
+        </is>
+      </c>
+      <c r="C39">
+        <v>45.8887545344619</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>10301</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>Osorno</t>
+        </is>
+      </c>
+      <c r="C40">
+        <v>45.7697194985491</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>10105</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>Frutillar</t>
+        </is>
+      </c>
+      <c r="C41">
+        <v>45.2459861540728</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>10302</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>Puerto Octay</t>
+        </is>
+      </c>
+      <c r="C42">
+        <v>45.1017175254294</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>10109</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>Puerto Varas</t>
+        </is>
+      </c>
+      <c r="C43">
+        <v>45.0505635804258</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>10107</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>Llanquihue</t>
+        </is>
+      </c>
+      <c r="C44">
+        <v>43.8041186948926</v>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>10305</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>Río Negro</t>
+        </is>
+      </c>
+      <c r="C45">
+        <v>43.558223746903</v>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>10106</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>Los Muermos</t>
+        </is>
+      </c>
+      <c r="C46">
+        <v>43.406816337571</v>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>10301</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>Osorno</t>
+        </is>
+      </c>
+      <c r="C47">
+        <v>43.3843863758219</v>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>10307</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>San Pablo</t>
+        </is>
+      </c>
+      <c r="C48">
+        <v>43.3591458406664</v>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>10208</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>Quellón</t>
+        </is>
+      </c>
+      <c r="C49">
+        <v>43.3000266453504</v>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>10302</t>
+        </is>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>Puerto Octay</t>
+        </is>
+      </c>
+      <c r="C50">
+        <v>43.2866079703429</v>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>10203</t>
+        </is>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>Chonchi</t>
+        </is>
+      </c>
+      <c r="C51">
+        <v>43.2156218633087</v>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>10304</t>
+        </is>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>Puyehue</t>
+        </is>
+      </c>
+      <c r="C52">
+        <v>43.0820895522388</v>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>10101</t>
+        </is>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>Puerto Montt</t>
+        </is>
+      </c>
+      <c r="C53">
+        <v>42.605796329583</v>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>10105</t>
+        </is>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>Frutillar</t>
+        </is>
+      </c>
+      <c r="C54">
+        <v>42.2360356595626</v>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
+          <t>10208</t>
+        </is>
+      </c>
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>Quellón</t>
+        </is>
+      </c>
+      <c r="C55">
+        <v>42.2077841946789</v>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="inlineStr">
+        <is>
+          <t>10201</t>
+        </is>
+      </c>
+      <c r="B56" t="inlineStr">
+        <is>
+          <t>Castro</t>
+        </is>
+      </c>
+      <c r="C56">
+        <v>42.1399685463941</v>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="inlineStr">
+        <is>
+          <t>10303</t>
+        </is>
+      </c>
+      <c r="B57" t="inlineStr">
+        <is>
+          <t>Purranque</t>
+        </is>
+      </c>
+      <c r="C57">
+        <v>41.8503906552178</v>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="inlineStr">
+        <is>
+          <t>10202</t>
+        </is>
+      </c>
+      <c r="B58" t="inlineStr">
+        <is>
+          <t>Ancud</t>
+        </is>
+      </c>
+      <c r="C58">
+        <v>41.7915844838922</v>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="inlineStr">
+        <is>
+          <t>10109</t>
+        </is>
+      </c>
+      <c r="B59" t="inlineStr">
+        <is>
+          <t>Puerto Varas</t>
+        </is>
+      </c>
+      <c r="C59">
+        <v>41.7879591538413</v>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="inlineStr">
+        <is>
+          <t>10301</t>
+        </is>
+      </c>
+      <c r="B60" t="inlineStr">
+        <is>
+          <t>Osorno</t>
+        </is>
+      </c>
+      <c r="C60">
+        <v>41.4719694520147</v>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="inlineStr">
+        <is>
+          <t>10206</t>
+        </is>
+      </c>
+      <c r="B61" t="inlineStr">
+        <is>
+          <t>Puqueldón</t>
+        </is>
+      </c>
+      <c r="C61">
+        <v>41.316685584563</v>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="inlineStr">
+        <is>
+          <t>10208</t>
+        </is>
+      </c>
+      <c r="B62" t="inlineStr">
+        <is>
+          <t>Quellón</t>
+        </is>
+      </c>
+      <c r="C62">
+        <v>40.3755868544601</v>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="inlineStr">
+        <is>
+          <t>10304</t>
+        </is>
+      </c>
+      <c r="B63" t="inlineStr">
+        <is>
+          <t>Puyehue</t>
+        </is>
+      </c>
+      <c r="C63">
+        <v>40.3171048829818</v>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="inlineStr">
+        <is>
+          <t>10107</t>
+        </is>
+      </c>
+      <c r="B64" t="inlineStr">
+        <is>
+          <t>Llanquihue</t>
+        </is>
+      </c>
+      <c r="C64">
+        <v>39.9711124167646</v>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="inlineStr">
+        <is>
+          <t>10206</t>
+        </is>
+      </c>
+      <c r="B65" t="inlineStr">
+        <is>
+          <t>Puqueldón</t>
+        </is>
+      </c>
+      <c r="C65">
+        <v>39.9234458586977</v>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="inlineStr">
+        <is>
+          <t>10307</t>
+        </is>
+      </c>
+      <c r="B66" t="inlineStr">
+        <is>
+          <t>San Pablo</t>
+        </is>
+      </c>
+      <c r="C66">
+        <v>39.7044936954952</v>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="inlineStr">
+        <is>
+          <t>10102</t>
+        </is>
+      </c>
+      <c r="B67" t="inlineStr">
+        <is>
+          <t>Calbuco</t>
+        </is>
+      </c>
+      <c r="C67">
+        <v>39.6964188709206</v>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="inlineStr">
+        <is>
+          <t>10205</t>
+        </is>
+      </c>
+      <c r="B68" t="inlineStr">
+        <is>
+          <t>Dalcahue</t>
+        </is>
+      </c>
+      <c r="C68">
+        <v>39.5839304480749</v>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="inlineStr">
+        <is>
+          <t>10203</t>
+        </is>
+      </c>
+      <c r="B69" t="inlineStr">
+        <is>
+          <t>Chonchi</t>
+        </is>
+      </c>
+      <c r="C69">
+        <v>39.560502283105</v>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="inlineStr">
+        <is>
+          <t>10201</t>
+        </is>
+      </c>
+      <c r="B70" t="inlineStr">
+        <is>
+          <t>Castro</t>
+        </is>
+      </c>
+      <c r="C70">
+        <v>39.4864019360456</v>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="inlineStr">
+        <is>
+          <t>10210</t>
+        </is>
+      </c>
+      <c r="B71" t="inlineStr">
+        <is>
+          <t>Quinchao</t>
+        </is>
+      </c>
+      <c r="C71">
+        <v>39.3926553672316</v>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" t="inlineStr">
+        <is>
+          <t>10305</t>
+        </is>
+      </c>
+      <c r="B72" t="inlineStr">
+        <is>
+          <t>Río Negro</t>
+        </is>
+      </c>
+      <c r="C72">
+        <v>39.3668332894852</v>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="inlineStr">
+        <is>
+          <t>10107</t>
+        </is>
+      </c>
+      <c r="B73" t="inlineStr">
+        <is>
+          <t>Llanquihue</t>
+        </is>
+      </c>
+      <c r="C73">
+        <v>39.3508533747091</v>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" t="inlineStr">
+        <is>
+          <t>10402</t>
+        </is>
+      </c>
+      <c r="B74" t="inlineStr">
+        <is>
+          <t>Futaleufú</t>
+        </is>
+      </c>
+      <c r="C74">
+        <v>39.2324561403509</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>10204</t>
+        </is>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>Curaco de Vélez</t>
+        </is>
+      </c>
+      <c r="C75">
+        <v>38.7440047961631</v>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" t="inlineStr">
+        <is>
+          <t>10303</t>
+        </is>
+      </c>
+      <c r="B76" t="inlineStr">
+        <is>
+          <t>Purranque</t>
+        </is>
+      </c>
+      <c r="C76">
+        <v>38.6090369519433</v>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" t="inlineStr">
+        <is>
+          <t>10109</t>
+        </is>
+      </c>
+      <c r="B77" t="inlineStr">
+        <is>
+          <t>Puerto Varas</t>
+        </is>
+      </c>
+      <c r="C77">
+        <v>38.4655371041614</v>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" t="inlineStr">
+        <is>
+          <t>10208</t>
+        </is>
+      </c>
+      <c r="B78" t="inlineStr">
+        <is>
+          <t>Quellón</t>
+        </is>
+      </c>
+      <c r="C78">
+        <v>38.3927617521367</v>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" t="inlineStr">
+        <is>
+          <t>10102</t>
+        </is>
+      </c>
+      <c r="B79" t="inlineStr">
+        <is>
+          <t>Calbuco</t>
+        </is>
+      </c>
+      <c r="C79">
+        <v>38.3849196639752</v>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" t="inlineStr">
+        <is>
+          <t>10101</t>
+        </is>
+      </c>
+      <c r="B80" t="inlineStr">
+        <is>
+          <t>Puerto Montt</t>
+        </is>
+      </c>
+      <c r="C80">
+        <v>38.0167901670195</v>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" t="inlineStr">
+        <is>
+          <t>10301</t>
+        </is>
+      </c>
+      <c r="B81" t="inlineStr">
+        <is>
+          <t>Osorno</t>
+        </is>
+      </c>
+      <c r="C81">
+        <v>37.7755037961187</v>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" t="inlineStr">
+        <is>
+          <t>10205</t>
+        </is>
+      </c>
+      <c r="B82" t="inlineStr">
+        <is>
+          <t>Dalcahue</t>
+        </is>
+      </c>
+      <c r="C82">
+        <v>37.7226640621366</v>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" t="inlineStr">
+        <is>
+          <t>10206</t>
+        </is>
+      </c>
+      <c r="B83" t="inlineStr">
+        <is>
+          <t>Puqueldón</t>
+        </is>
+      </c>
+      <c r="C83">
+        <v>37.4700239808153</v>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" t="inlineStr">
+        <is>
+          <t>10208</t>
+        </is>
+      </c>
+      <c r="B84" t="inlineStr">
+        <is>
+          <t>Quellón</t>
+        </is>
+      </c>
+      <c r="C84">
+        <v>37.4005730942147</v>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" t="inlineStr">
+        <is>
+          <t>10201</t>
+        </is>
+      </c>
+      <c r="B85" t="inlineStr">
+        <is>
+          <t>Castro</t>
+        </is>
+      </c>
+      <c r="C85">
+        <v>36.9101630094956</v>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" t="inlineStr">
+        <is>
+          <t>10404</t>
+        </is>
+      </c>
+      <c r="B86" t="inlineStr">
+        <is>
+          <t>Palena</t>
+        </is>
+      </c>
+      <c r="C86">
+        <v>36.7932862190813</v>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" t="inlineStr">
+        <is>
+          <t>10105</t>
+        </is>
+      </c>
+      <c r="B87" t="inlineStr">
+        <is>
+          <t>Frutillar</t>
+        </is>
+      </c>
+      <c r="C87">
+        <v>36.6877582644628</v>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" t="inlineStr">
+        <is>
+          <t>10203</t>
+        </is>
+      </c>
+      <c r="B88" t="inlineStr">
+        <is>
+          <t>Chonchi</t>
+        </is>
+      </c>
+      <c r="C88">
+        <v>36.6537984282366</v>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" t="inlineStr">
+        <is>
+          <t>10403</t>
+        </is>
+      </c>
+      <c r="B89" t="inlineStr">
+        <is>
+          <t>Hualaihué</t>
+        </is>
+      </c>
+      <c r="C89">
+        <v>36.3651229722658</v>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" t="inlineStr">
+        <is>
+          <t>10107</t>
+        </is>
+      </c>
+      <c r="B90" t="inlineStr">
+        <is>
+          <t>Llanquihue</t>
+        </is>
+      </c>
+      <c r="C90">
+        <v>35.9745553359684</v>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" t="inlineStr">
+        <is>
+          <t>10202</t>
+        </is>
+      </c>
+      <c r="B91" t="inlineStr">
+        <is>
+          <t>Ancud</t>
+        </is>
+      </c>
+      <c r="C91">
+        <v>35.8258466934697</v>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" t="inlineStr">
+        <is>
+          <t>10301</t>
+        </is>
+      </c>
+      <c r="B92" t="inlineStr">
+        <is>
+          <t>Osorno</t>
+        </is>
+      </c>
+      <c r="C92">
+        <v>35.8024113442788</v>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" t="inlineStr">
+        <is>
+          <t>10403</t>
+        </is>
+      </c>
+      <c r="B93" t="inlineStr">
+        <is>
+          <t>Hualaihué</t>
+        </is>
+      </c>
+      <c r="C93">
+        <v>35.7656190111154</v>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" t="inlineStr">
+        <is>
+          <t>10404</t>
+        </is>
+      </c>
+      <c r="B94" t="inlineStr">
+        <is>
+          <t>Palena</t>
+        </is>
+      </c>
+      <c r="C94">
+        <v>35.567081604426</v>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" t="inlineStr">
+        <is>
+          <t>10209</t>
+        </is>
+      </c>
+      <c r="B95" t="inlineStr">
+        <is>
+          <t>Quemchi</t>
+        </is>
+      </c>
+      <c r="C95">
+        <v>35.5373312831027</v>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" t="inlineStr">
+        <is>
+          <t>10203</t>
+        </is>
+      </c>
+      <c r="B96" t="inlineStr">
+        <is>
+          <t>Chonchi</t>
+        </is>
+      </c>
+      <c r="C96">
+        <v>35.3810489713127</v>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" t="inlineStr">
+        <is>
+          <t>10101</t>
+        </is>
+      </c>
+      <c r="B97" t="inlineStr">
+        <is>
+          <t>Puerto Montt</t>
+        </is>
+      </c>
+      <c r="C97">
+        <v>35.2583569340658</v>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" t="inlineStr">
+        <is>
+          <t>10205</t>
+        </is>
+      </c>
+      <c r="B98" t="inlineStr">
+        <is>
+          <t>Dalcahue</t>
+        </is>
+      </c>
+      <c r="C98">
+        <v>35.2048417132216</v>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" t="inlineStr">
+        <is>
+          <t>10302</t>
+        </is>
+      </c>
+      <c r="B99" t="inlineStr">
+        <is>
+          <t>Puerto Octay</t>
+        </is>
+      </c>
+      <c r="C99">
+        <v>35.1250762660159</v>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" t="inlineStr">
+        <is>
+          <t>10210</t>
+        </is>
+      </c>
+      <c r="B100" t="inlineStr">
+        <is>
+          <t>Quinchao</t>
+        </is>
+      </c>
+      <c r="C100">
+        <v>34.9659005979073</v>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" t="inlineStr">
+        <is>
+          <t>10209</t>
+        </is>
+      </c>
+      <c r="B101" t="inlineStr">
+        <is>
+          <t>Quemchi</t>
+        </is>
+      </c>
+      <c r="C101">
+        <v>34.9551882913994</v>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" t="inlineStr">
+        <is>
+          <t>10207</t>
+        </is>
+      </c>
+      <c r="B102" t="inlineStr">
+        <is>
+          <t>Queilén</t>
+        </is>
+      </c>
+      <c r="C102">
+        <v>34.9090189873418</v>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" t="inlineStr">
+        <is>
+          <t>10107</t>
+        </is>
+      </c>
+      <c r="B103" t="inlineStr">
+        <is>
+          <t>Llanquihue</t>
+        </is>
+      </c>
+      <c r="C103">
+        <v>34.8738478983869</v>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" t="inlineStr">
+        <is>
+          <t>10103</t>
+        </is>
+      </c>
+      <c r="B104" t="inlineStr">
+        <is>
+          <t>Cochamó</t>
+        </is>
+      </c>
+      <c r="C104">
+        <v>34.7269624573379</v>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" t="inlineStr">
+        <is>
+          <t>10209</t>
+        </is>
+      </c>
+      <c r="B105" t="inlineStr">
+        <is>
+          <t>Quemchi</t>
+        </is>
+      </c>
+      <c r="C105">
+        <v>34.4635908838243</v>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" t="inlineStr">
+        <is>
+          <t>10205</t>
+        </is>
+      </c>
+      <c r="B106" t="inlineStr">
+        <is>
+          <t>Dalcahue</t>
+        </is>
+      </c>
+      <c r="C106">
+        <v>34.4357169936499</v>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" t="inlineStr">
+        <is>
+          <t>10401</t>
+        </is>
+      </c>
+      <c r="B107" t="inlineStr">
+        <is>
+          <t>Chaitén</t>
+        </is>
+      </c>
+      <c r="C107">
+        <v>34.0283939662822</v>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108" t="inlineStr">
+        <is>
+          <t>10202</t>
+        </is>
+      </c>
+      <c r="B108" t="inlineStr">
+        <is>
+          <t>Ancud</t>
+        </is>
+      </c>
+      <c r="C108">
+        <v>34.009577028319</v>
+      </c>
+    </row>
+    <row r="109">
+      <c r="A109" t="inlineStr">
+        <is>
+          <t>10307</t>
+        </is>
+      </c>
+      <c r="B109" t="inlineStr">
+        <is>
+          <t>San Pablo</t>
+        </is>
+      </c>
+      <c r="C109">
+        <v>33.9868701206529</v>
+      </c>
+    </row>
+    <row r="110">
+      <c r="A110" t="inlineStr">
+        <is>
+          <t>10402</t>
+        </is>
+      </c>
+      <c r="B110" t="inlineStr">
+        <is>
+          <t>Futaleufú</t>
+        </is>
+      </c>
+      <c r="C110">
+        <v>33.8514680483592</v>
+      </c>
+    </row>
+    <row r="111">
+      <c r="A111" t="inlineStr">
+        <is>
+          <t>10107</t>
+        </is>
+      </c>
+      <c r="B111" t="inlineStr">
+        <is>
+          <t>Llanquihue</t>
+        </is>
+      </c>
+      <c r="C111">
+        <v>33.8464670508644</v>
+      </c>
+    </row>
+    <row r="112">
+      <c r="A112" t="inlineStr">
+        <is>
+          <t>10304</t>
+        </is>
+      </c>
+      <c r="B112" t="inlineStr">
+        <is>
+          <t>Puyehue</t>
+        </is>
+      </c>
+      <c r="C112">
+        <v>33.7195073813847</v>
+      </c>
+    </row>
+    <row r="113">
+      <c r="A113" t="inlineStr">
+        <is>
+          <t>10203</t>
+        </is>
+      </c>
+      <c r="B113" t="inlineStr">
+        <is>
+          <t>Chonchi</t>
+        </is>
+      </c>
+      <c r="C113">
+        <v>33.7091775372375</v>
+      </c>
+    </row>
+    <row r="114">
+      <c r="A114" t="inlineStr">
+        <is>
+          <t>10305</t>
+        </is>
+      </c>
+      <c r="B114" t="inlineStr">
+        <is>
+          <t>Río Negro</t>
+        </is>
+      </c>
+      <c r="C114">
+        <v>33.4649713111851</v>
+      </c>
+    </row>
+    <row r="115">
+      <c r="A115" t="inlineStr">
+        <is>
+          <t>10204</t>
+        </is>
+      </c>
+      <c r="B115" t="inlineStr">
+        <is>
+          <t>Curaco de Vélez</t>
+        </is>
+      </c>
+      <c r="C115">
+        <v>33.4300077339521</v>
+      </c>
+    </row>
+    <row r="116">
+      <c r="A116" t="inlineStr">
+        <is>
+          <t>10201</t>
+        </is>
+      </c>
+      <c r="B116" t="inlineStr">
+        <is>
+          <t>Castro</t>
+        </is>
+      </c>
+      <c r="C116">
+        <v>33.3765575627497</v>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" t="inlineStr">
+        <is>
+          <t>10102</t>
+        </is>
+      </c>
+      <c r="B117" t="inlineStr">
+        <is>
+          <t>Calbuco</t>
+        </is>
+      </c>
+      <c r="C117">
+        <v>33.1737316990126</v>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118" t="inlineStr">
+        <is>
+          <t>10102</t>
+        </is>
+      </c>
+      <c r="B118" t="inlineStr">
+        <is>
+          <t>Calbuco</t>
+        </is>
+      </c>
+      <c r="C118">
+        <v>33.1238849416257</v>
+      </c>
+    </row>
+    <row r="119">
+      <c r="A119" t="inlineStr">
+        <is>
+          <t>10107</t>
+        </is>
+      </c>
+      <c r="B119" t="inlineStr">
+        <is>
+          <t>Llanquihue</t>
+        </is>
+      </c>
+      <c r="C119">
+        <v>33.1048738033072</v>
+      </c>
+    </row>
+    <row r="120">
+      <c r="A120" t="inlineStr">
+        <is>
+          <t>10307</t>
+        </is>
+      </c>
+      <c r="B120" t="inlineStr">
+        <is>
+          <t>San Pablo</t>
+        </is>
+      </c>
+      <c r="C120">
+        <v>33.0639730639731</v>
+      </c>
+    </row>
+    <row r="121">
+      <c r="A121" t="inlineStr">
+        <is>
+          <t>10207</t>
+        </is>
+      </c>
+      <c r="B121" t="inlineStr">
+        <is>
+          <t>Queilén</t>
+        </is>
+      </c>
+      <c r="C121">
+        <v>33.0513307984791</v>
+      </c>
+    </row>
+    <row r="122">
+      <c r="A122" t="inlineStr">
+        <is>
+          <t>10404</t>
+        </is>
+      </c>
+      <c r="B122" t="inlineStr">
+        <is>
+          <t>Palena</t>
+        </is>
+      </c>
+      <c r="C122">
+        <v>33.0411572530396</v>
+      </c>
+    </row>
+    <row r="123">
+      <c r="A123" t="inlineStr">
+        <is>
+          <t>10302</t>
+        </is>
+      </c>
+      <c r="B123" t="inlineStr">
+        <is>
+          <t>Puerto Octay</t>
+        </is>
+      </c>
+      <c r="C123">
+        <v>32.7528184418644</v>
+      </c>
+    </row>
+    <row r="124">
+      <c r="A124" t="inlineStr">
+        <is>
+          <t>10109</t>
+        </is>
+      </c>
+      <c r="B124" t="inlineStr">
+        <is>
+          <t>Puerto Varas</t>
+        </is>
+      </c>
+      <c r="C124">
+        <v>32.6649588573203</v>
+      </c>
+    </row>
+    <row r="125">
+      <c r="A125" t="inlineStr">
+        <is>
+          <t>10401</t>
+        </is>
+      </c>
+      <c r="B125" t="inlineStr">
+        <is>
+          <t>Chaitén</t>
+        </is>
+      </c>
+      <c r="C125">
+        <v>32.6382727003845</v>
+      </c>
+    </row>
+    <row r="126">
+      <c r="A126" t="inlineStr">
+        <is>
+          <t>10301</t>
+        </is>
+      </c>
+      <c r="B126" t="inlineStr">
+        <is>
+          <t>Osorno</t>
+        </is>
+      </c>
+      <c r="C126">
+        <v>32.5919188758057</v>
+      </c>
+    </row>
+    <row r="127">
+      <c r="A127" t="inlineStr">
+        <is>
+          <t>10104</t>
+        </is>
+      </c>
+      <c r="B127" t="inlineStr">
+        <is>
+          <t>Fresia</t>
+        </is>
+      </c>
+      <c r="C127">
+        <v>32.5389948006932</v>
+      </c>
+    </row>
+    <row r="128">
+      <c r="A128" t="inlineStr">
+        <is>
+          <t>10206</t>
+        </is>
+      </c>
+      <c r="B128" t="inlineStr">
+        <is>
+          <t>Puqueldón</t>
+        </is>
+      </c>
+      <c r="C128">
+        <v>32.5166574125486</v>
+      </c>
+    </row>
+    <row r="129">
+      <c r="A129" t="inlineStr">
+        <is>
+          <t>10404</t>
+        </is>
+      </c>
+      <c r="B129" t="inlineStr">
+        <is>
+          <t>Palena</t>
+        </is>
+      </c>
+      <c r="C129">
+        <v>32.2678117048346</v>
+      </c>
+    </row>
+    <row r="130">
+      <c r="A130" t="inlineStr">
+        <is>
+          <t>10202</t>
+        </is>
+      </c>
+      <c r="B130" t="inlineStr">
+        <is>
+          <t>Ancud</t>
+        </is>
+      </c>
+      <c r="C130">
+        <v>32.2067300586294</v>
+      </c>
+    </row>
+    <row r="131">
+      <c r="A131" t="inlineStr">
+        <is>
+          <t>10303</t>
+        </is>
+      </c>
+      <c r="B131" t="inlineStr">
+        <is>
+          <t>Purranque</t>
+        </is>
+      </c>
+      <c r="C131">
+        <v>31.7806395143118</v>
+      </c>
+    </row>
+    <row r="132">
+      <c r="A132" t="inlineStr">
+        <is>
+          <t>10105</t>
+        </is>
+      </c>
+      <c r="B132" t="inlineStr">
+        <is>
+          <t>Frutillar</t>
+        </is>
+      </c>
+      <c r="C132">
+        <v>31.7224287484511</v>
+      </c>
+    </row>
+    <row r="133">
+      <c r="A133" t="inlineStr">
+        <is>
+          <t>10403</t>
+        </is>
+      </c>
+      <c r="B133" t="inlineStr">
+        <is>
+          <t>Hualaihué</t>
+        </is>
+      </c>
+      <c r="C133">
+        <v>31.3852592895059</v>
+      </c>
+    </row>
+    <row r="134">
+      <c r="A134" t="inlineStr">
+        <is>
+          <t>10105</t>
+        </is>
+      </c>
+      <c r="B134" t="inlineStr">
+        <is>
+          <t>Frutillar</t>
+        </is>
+      </c>
+      <c r="C134">
+        <v>31.2619193570358</v>
+      </c>
+    </row>
+    <row r="135">
+      <c r="A135" t="inlineStr">
+        <is>
+          <t>10108</t>
+        </is>
+      </c>
+      <c r="B135" t="inlineStr">
+        <is>
+          <t>Maullín</t>
+        </is>
+      </c>
+      <c r="C135">
+        <v>31.2581974892262</v>
+      </c>
+    </row>
+    <row r="136">
+      <c r="A136" t="inlineStr">
+        <is>
+          <t>10305</t>
+        </is>
+      </c>
+      <c r="B136" t="inlineStr">
+        <is>
+          <t>Río Negro</t>
+        </is>
+      </c>
+      <c r="C136">
+        <v>31.2547735951991</v>
+      </c>
+    </row>
+    <row r="137">
+      <c r="A137" t="inlineStr">
+        <is>
+          <t>10301</t>
+        </is>
+      </c>
+      <c r="B137" t="inlineStr">
+        <is>
+          <t>Osorno</t>
+        </is>
+      </c>
+      <c r="C137">
+        <v>31.2546170318213</v>
+      </c>
+    </row>
+    <row r="138">
+      <c r="A138" t="inlineStr">
+        <is>
+          <t>10404</t>
+        </is>
+      </c>
+      <c r="B138" t="inlineStr">
+        <is>
+          <t>Palena</t>
+        </is>
+      </c>
+      <c r="C138">
+        <v>31.2481008811911</v>
+      </c>
+    </row>
+    <row r="139">
+      <c r="A139" t="inlineStr">
+        <is>
+          <t>10205</t>
+        </is>
+      </c>
+      <c r="B139" t="inlineStr">
+        <is>
+          <t>Dalcahue</t>
+        </is>
+      </c>
+      <c r="C139">
+        <v>31.0220740955417</v>
+      </c>
+    </row>
+    <row r="140">
+      <c r="A140" t="inlineStr">
+        <is>
+          <t>10301</t>
+        </is>
+      </c>
+      <c r="B140" t="inlineStr">
+        <is>
+          <t>Osorno</t>
+        </is>
+      </c>
+      <c r="C140">
+        <v>30.9877213039575</v>
+      </c>
+    </row>
+    <row r="141">
+      <c r="A141" t="inlineStr">
+        <is>
+          <t>10104</t>
+        </is>
+      </c>
+      <c r="B141" t="inlineStr">
+        <is>
+          <t>Fresia</t>
+        </is>
+      </c>
+      <c r="C141">
+        <v>30.8925177121134</v>
+      </c>
+    </row>
+    <row r="142">
+      <c r="A142" t="inlineStr">
+        <is>
+          <t>10108</t>
+        </is>
+      </c>
+      <c r="B142" t="inlineStr">
+        <is>
+          <t>Maullín</t>
+        </is>
+      </c>
+      <c r="C142">
+        <v>30.8522369250158</v>
+      </c>
+    </row>
+    <row r="143">
+      <c r="A143" t="inlineStr">
+        <is>
+          <t>10304</t>
+        </is>
+      </c>
+      <c r="B143" t="inlineStr">
+        <is>
+          <t>Puyehue</t>
+        </is>
+      </c>
+      <c r="C143">
+        <v>30.5927230046948</v>
+      </c>
+    </row>
+    <row r="144">
+      <c r="A144" t="inlineStr">
+        <is>
+          <t>10108</t>
+        </is>
+      </c>
+      <c r="B144" t="inlineStr">
+        <is>
+          <t>Maullín</t>
+        </is>
+      </c>
+      <c r="C144">
+        <v>30.5174291938998</v>
+      </c>
+    </row>
+    <row r="145">
+      <c r="A145" t="inlineStr">
+        <is>
+          <t>10209</t>
+        </is>
+      </c>
+      <c r="B145" t="inlineStr">
+        <is>
+          <t>Quemchi</t>
+        </is>
+      </c>
+      <c r="C145">
+        <v>30.5110941734417</v>
+      </c>
+    </row>
+    <row r="146">
+      <c r="A146" t="inlineStr">
+        <is>
           <t>10306</t>
         </is>
       </c>
-      <c r="B31" t="inlineStr">
+      <c r="B146" t="inlineStr">
         <is>
           <t>San Juan de la Costa</t>
         </is>
       </c>
-      <c r="C31">
+      <c r="C146">
+        <v>30.4624346172135</v>
+      </c>
+    </row>
+    <row r="147">
+      <c r="A147" t="inlineStr">
+        <is>
+          <t>10207</t>
+        </is>
+      </c>
+      <c r="B147" t="inlineStr">
+        <is>
+          <t>Queilén</t>
+        </is>
+      </c>
+      <c r="C147">
+        <v>30.3467000835422</v>
+      </c>
+    </row>
+    <row r="148">
+      <c r="A148" t="inlineStr">
+        <is>
+          <t>10404</t>
+        </is>
+      </c>
+      <c r="B148" t="inlineStr">
+        <is>
+          <t>Palena</t>
+        </is>
+      </c>
+      <c r="C148">
+        <v>30.3155904595695</v>
+      </c>
+    </row>
+    <row r="149">
+      <c r="A149" t="inlineStr">
+        <is>
+          <t>10301</t>
+        </is>
+      </c>
+      <c r="B149" t="inlineStr">
+        <is>
+          <t>Osorno</t>
+        </is>
+      </c>
+      <c r="C149">
+        <v>30.2595887524085</v>
+      </c>
+    </row>
+    <row r="150">
+      <c r="A150" t="inlineStr">
+        <is>
+          <t>10404</t>
+        </is>
+      </c>
+      <c r="B150" t="inlineStr">
+        <is>
+          <t>Palena</t>
+        </is>
+      </c>
+      <c r="C150">
+        <v>30.231066036567</v>
+      </c>
+    </row>
+    <row r="151">
+      <c r="A151" t="inlineStr">
+        <is>
+          <t>10202</t>
+        </is>
+      </c>
+      <c r="B151" t="inlineStr">
+        <is>
+          <t>Ancud</t>
+        </is>
+      </c>
+      <c r="C151">
+        <v>30.20176312198</v>
+      </c>
+    </row>
+    <row r="152">
+      <c r="A152" t="inlineStr">
+        <is>
+          <t>10207</t>
+        </is>
+      </c>
+      <c r="B152" t="inlineStr">
+        <is>
+          <t>Queilén</t>
+        </is>
+      </c>
+      <c r="C152">
+        <v>30.0845245088441</v>
+      </c>
+    </row>
+    <row r="153">
+      <c r="A153" t="inlineStr">
+        <is>
+          <t>10401</t>
+        </is>
+      </c>
+      <c r="B153" t="inlineStr">
+        <is>
+          <t>Chaitén</t>
+        </is>
+      </c>
+      <c r="C153">
+        <v>30.0059382422803</v>
+      </c>
+    </row>
+    <row r="154">
+      <c r="A154" t="inlineStr">
+        <is>
+          <t>10210</t>
+        </is>
+      </c>
+      <c r="B154" t="inlineStr">
+        <is>
+          <t>Quinchao</t>
+        </is>
+      </c>
+      <c r="C154">
+        <v>29.7960396945169</v>
+      </c>
+    </row>
+    <row r="155">
+      <c r="A155" t="inlineStr">
+        <is>
+          <t>10303</t>
+        </is>
+      </c>
+      <c r="B155" t="inlineStr">
+        <is>
+          <t>Purranque</t>
+        </is>
+      </c>
+      <c r="C155">
+        <v>29.5029805058805</v>
+      </c>
+    </row>
+    <row r="156">
+      <c r="A156" t="inlineStr">
+        <is>
+          <t>10106</t>
+        </is>
+      </c>
+      <c r="B156" t="inlineStr">
+        <is>
+          <t>Los Muermos</t>
+        </is>
+      </c>
+      <c r="C156">
+        <v>29.1190657527291</v>
+      </c>
+    </row>
+    <row r="157">
+      <c r="A157" t="inlineStr">
+        <is>
+          <t>10204</t>
+        </is>
+      </c>
+      <c r="B157" t="inlineStr">
+        <is>
+          <t>Curaco de Vélez</t>
+        </is>
+      </c>
+      <c r="C157">
+        <v>28.4503745318352</v>
+      </c>
+    </row>
+    <row r="158">
+      <c r="A158" t="inlineStr">
+        <is>
+          <t>10106</t>
+        </is>
+      </c>
+      <c r="B158" t="inlineStr">
+        <is>
+          <t>Los Muermos</t>
+        </is>
+      </c>
+      <c r="C158">
+        <v>27.8625165343915</v>
+      </c>
+    </row>
+    <row r="159">
+      <c r="A159" t="inlineStr">
+        <is>
+          <t>10102</t>
+        </is>
+      </c>
+      <c r="B159" t="inlineStr">
+        <is>
+          <t>Calbuco</t>
+        </is>
+      </c>
+      <c r="C159">
+        <v>27.6109437429225</v>
+      </c>
+    </row>
+    <row r="160">
+      <c r="A160" t="inlineStr">
+        <is>
+          <t>10404</t>
+        </is>
+      </c>
+      <c r="B160" t="inlineStr">
+        <is>
+          <t>Palena</t>
+        </is>
+      </c>
+      <c r="C160">
+        <v>27.5106837606838</v>
+      </c>
+    </row>
+    <row r="161">
+      <c r="A161" t="inlineStr">
+        <is>
+          <t>10307</t>
+        </is>
+      </c>
+      <c r="B161" t="inlineStr">
+        <is>
+          <t>San Pablo</t>
+        </is>
+      </c>
+      <c r="C161">
+        <v>27.4773920192247</v>
+      </c>
+    </row>
+    <row r="162">
+      <c r="A162" t="inlineStr">
+        <is>
+          <t>10108</t>
+        </is>
+      </c>
+      <c r="B162" t="inlineStr">
+        <is>
+          <t>Maullín</t>
+        </is>
+      </c>
+      <c r="C162">
+        <v>27.2995422153004</v>
+      </c>
+    </row>
+    <row r="163">
+      <c r="A163" t="inlineStr">
+        <is>
+          <t>10404</t>
+        </is>
+      </c>
+      <c r="B163" t="inlineStr">
+        <is>
+          <t>Palena</t>
+        </is>
+      </c>
+      <c r="C163">
+        <v>27.1187705162638</v>
+      </c>
+    </row>
+    <row r="164">
+      <c r="A164" t="inlineStr">
+        <is>
+          <t>10401</t>
+        </is>
+      </c>
+      <c r="B164" t="inlineStr">
+        <is>
+          <t>Chaitén</t>
+        </is>
+      </c>
+      <c r="C164">
+        <v>26.9725630538514</v>
+      </c>
+    </row>
+    <row r="165">
+      <c r="A165" t="inlineStr">
+        <is>
+          <t>10207</t>
+        </is>
+      </c>
+      <c r="B165" t="inlineStr">
+        <is>
+          <t>Queilén</t>
+        </is>
+      </c>
+      <c r="C165">
+        <v>26.9344637330104</v>
+      </c>
+    </row>
+    <row r="166">
+      <c r="A166" t="inlineStr">
+        <is>
+          <t>10401</t>
+        </is>
+      </c>
+      <c r="B166" t="inlineStr">
+        <is>
+          <t>Chaitén</t>
+        </is>
+      </c>
+      <c r="C166">
+        <v>26.7156862745098</v>
+      </c>
+    </row>
+    <row r="167">
+      <c r="A167" t="inlineStr">
+        <is>
+          <t>10104</t>
+        </is>
+      </c>
+      <c r="B167" t="inlineStr">
+        <is>
+          <t>Fresia</t>
+        </is>
+      </c>
+      <c r="C167">
+        <v>26.6835901027078</v>
+      </c>
+    </row>
+    <row r="168">
+      <c r="A168" t="inlineStr">
+        <is>
+          <t>10305</t>
+        </is>
+      </c>
+      <c r="B168" t="inlineStr">
+        <is>
+          <t>Río Negro</t>
+        </is>
+      </c>
+      <c r="C168">
+        <v>26.5784088002047</v>
+      </c>
+    </row>
+    <row r="169">
+      <c r="A169" t="inlineStr">
+        <is>
+          <t>10104</t>
+        </is>
+      </c>
+      <c r="B169" t="inlineStr">
+        <is>
+          <t>Fresia</t>
+        </is>
+      </c>
+      <c r="C169">
+        <v>26.4916315318768</v>
+      </c>
+    </row>
+    <row r="170">
+      <c r="A170" t="inlineStr">
+        <is>
+          <t>10403</t>
+        </is>
+      </c>
+      <c r="B170" t="inlineStr">
+        <is>
+          <t>Hualaihué</t>
+        </is>
+      </c>
+      <c r="C170">
+        <v>26.4805042509528</v>
+      </c>
+    </row>
+    <row r="171">
+      <c r="A171" t="inlineStr">
+        <is>
+          <t>10403</t>
+        </is>
+      </c>
+      <c r="B171" t="inlineStr">
+        <is>
+          <t>Hualaihué</t>
+        </is>
+      </c>
+      <c r="C171">
+        <v>26.3925294888598</v>
+      </c>
+    </row>
+    <row r="172">
+      <c r="A172" t="inlineStr">
+        <is>
+          <t>10106</t>
+        </is>
+      </c>
+      <c r="B172" t="inlineStr">
+        <is>
+          <t>Los Muermos</t>
+        </is>
+      </c>
+      <c r="C172">
+        <v>26.2889937980191</v>
+      </c>
+    </row>
+    <row r="173">
+      <c r="A173" t="inlineStr">
+        <is>
+          <t>10404</t>
+        </is>
+      </c>
+      <c r="B173" t="inlineStr">
+        <is>
+          <t>Palena</t>
+        </is>
+      </c>
+      <c r="C173">
+        <v>26.104673619158</v>
+      </c>
+    </row>
+    <row r="174">
+      <c r="A174" t="inlineStr">
+        <is>
+          <t>10302</t>
+        </is>
+      </c>
+      <c r="B174" t="inlineStr">
+        <is>
+          <t>Puerto Octay</t>
+        </is>
+      </c>
+      <c r="C174">
+        <v>26.0440835266821</v>
+      </c>
+    </row>
+    <row r="175">
+      <c r="A175" t="inlineStr">
+        <is>
+          <t>10402</t>
+        </is>
+      </c>
+      <c r="B175" t="inlineStr">
+        <is>
+          <t>Futaleufú</t>
+        </is>
+      </c>
+      <c r="C175">
+        <v>25.8000984736583</v>
+      </c>
+    </row>
+    <row r="176">
+      <c r="A176" t="inlineStr">
+        <is>
+          <t>10209</t>
+        </is>
+      </c>
+      <c r="B176" t="inlineStr">
+        <is>
+          <t>Quemchi</t>
+        </is>
+      </c>
+      <c r="C176">
+        <v>25.7922996333159</v>
+      </c>
+    </row>
+    <row r="177">
+      <c r="A177" t="inlineStr">
+        <is>
+          <t>10304</t>
+        </is>
+      </c>
+      <c r="B177" t="inlineStr">
+        <is>
+          <t>Puyehue</t>
+        </is>
+      </c>
+      <c r="C177">
+        <v>25.7702349869452</v>
+      </c>
+    </row>
+    <row r="178">
+      <c r="A178" t="inlineStr">
+        <is>
+          <t>10204</t>
+        </is>
+      </c>
+      <c r="B178" t="inlineStr">
+        <is>
+          <t>Curaco de Vélez</t>
+        </is>
+      </c>
+      <c r="C178">
+        <v>25.6082725060827</v>
+      </c>
+    </row>
+    <row r="179">
+      <c r="A179" t="inlineStr">
+        <is>
+          <t>10103</t>
+        </is>
+      </c>
+      <c r="B179" t="inlineStr">
+        <is>
+          <t>Cochamó</t>
+        </is>
+      </c>
+      <c r="C179">
+        <v>25.5699481865285</v>
+      </c>
+    </row>
+    <row r="180">
+      <c r="A180" t="inlineStr">
+        <is>
+          <t>10402</t>
+        </is>
+      </c>
+      <c r="B180" t="inlineStr">
+        <is>
+          <t>Futaleufú</t>
+        </is>
+      </c>
+      <c r="C180">
+        <v>25.4494239777187</v>
+      </c>
+    </row>
+    <row r="181">
+      <c r="A181" t="inlineStr">
+        <is>
+          <t>10303</t>
+        </is>
+      </c>
+      <c r="B181" t="inlineStr">
+        <is>
+          <t>Purranque</t>
+        </is>
+      </c>
+      <c r="C181">
+        <v>25.3154231020231</v>
+      </c>
+    </row>
+    <row r="182">
+      <c r="A182" t="inlineStr">
+        <is>
+          <t>10106</t>
+        </is>
+      </c>
+      <c r="B182" t="inlineStr">
+        <is>
+          <t>Los Muermos</t>
+        </is>
+      </c>
+      <c r="C182">
+        <v>25.1015297855775</v>
+      </c>
+    </row>
+    <row r="183">
+      <c r="A183" t="inlineStr">
+        <is>
+          <t>10402</t>
+        </is>
+      </c>
+      <c r="B183" t="inlineStr">
+        <is>
+          <t>Futaleufú</t>
+        </is>
+      </c>
+      <c r="C183">
+        <v>25.0781860828772</v>
+      </c>
+    </row>
+    <row r="184">
+      <c r="A184" t="inlineStr">
+        <is>
+          <t>10206</t>
+        </is>
+      </c>
+      <c r="B184" t="inlineStr">
+        <is>
+          <t>Puqueldón</t>
+        </is>
+      </c>
+      <c r="C184">
+        <v>25.0603528319406</v>
+      </c>
+    </row>
+    <row r="185">
+      <c r="A185" t="inlineStr">
+        <is>
+          <t>10210</t>
+        </is>
+      </c>
+      <c r="B185" t="inlineStr">
+        <is>
+          <t>Quinchao</t>
+        </is>
+      </c>
+      <c r="C185">
+        <v>24.8433940774487</v>
+      </c>
+    </row>
+    <row r="186">
+      <c r="A186" t="inlineStr">
+        <is>
+          <t>10210</t>
+        </is>
+      </c>
+      <c r="B186" t="inlineStr">
+        <is>
+          <t>Quinchao</t>
+        </is>
+      </c>
+      <c r="C186">
+        <v>24.8387530233808</v>
+      </c>
+    </row>
+    <row r="187">
+      <c r="A187" t="inlineStr">
+        <is>
+          <t>10103</t>
+        </is>
+      </c>
+      <c r="B187" t="inlineStr">
+        <is>
+          <t>Cochamó</t>
+        </is>
+      </c>
+      <c r="C187">
+        <v>24.4393862755016</v>
+      </c>
+    </row>
+    <row r="188">
+      <c r="A188" t="inlineStr">
+        <is>
+          <t>10103</t>
+        </is>
+      </c>
+      <c r="B188" t="inlineStr">
+        <is>
+          <t>Cochamó</t>
+        </is>
+      </c>
+      <c r="C188">
+        <v>23.8529962546816</v>
+      </c>
+    </row>
+    <row r="189">
+      <c r="A189" t="inlineStr">
+        <is>
+          <t>10108</t>
+        </is>
+      </c>
+      <c r="B189" t="inlineStr">
+        <is>
+          <t>Maullín</t>
+        </is>
+      </c>
+      <c r="C189">
+        <v>23.3841765873016</v>
+      </c>
+    </row>
+    <row r="190">
+      <c r="A190" t="inlineStr">
+        <is>
+          <t>10306</t>
+        </is>
+      </c>
+      <c r="B190" t="inlineStr">
+        <is>
+          <t>San Juan de la Costa</t>
+        </is>
+      </c>
+      <c r="C190">
+        <v>23.0342170858826</v>
+      </c>
+    </row>
+    <row r="191">
+      <c r="A191" t="inlineStr">
+        <is>
+          <t>10402</t>
+        </is>
+      </c>
+      <c r="B191" t="inlineStr">
+        <is>
+          <t>Futaleufú</t>
+        </is>
+      </c>
+      <c r="C191">
+        <v>22.7321524422974</v>
+      </c>
+    </row>
+    <row r="192">
+      <c r="A192" t="inlineStr">
+        <is>
+          <t>10104</t>
+        </is>
+      </c>
+      <c r="B192" t="inlineStr">
+        <is>
+          <t>Fresia</t>
+        </is>
+      </c>
+      <c r="C192">
+        <v>22.3626633552126</v>
+      </c>
+    </row>
+    <row r="193">
+      <c r="A193" t="inlineStr">
+        <is>
+          <t>10106</t>
+        </is>
+      </c>
+      <c r="B193" t="inlineStr">
+        <is>
+          <t>Los Muermos</t>
+        </is>
+      </c>
+      <c r="C193">
+        <v>22.2386524366722</v>
+      </c>
+    </row>
+    <row r="194">
+      <c r="A194" t="inlineStr">
+        <is>
+          <t>10103</t>
+        </is>
+      </c>
+      <c r="B194" t="inlineStr">
+        <is>
+          <t>Cochamó</t>
+        </is>
+      </c>
+      <c r="C194">
+        <v>20.961266984295</v>
+      </c>
+    </row>
+    <row r="195">
+      <c r="A195" t="inlineStr">
+        <is>
+          <t>10306</t>
+        </is>
+      </c>
+      <c r="B195" t="inlineStr">
+        <is>
+          <t>San Juan de la Costa</t>
+        </is>
+      </c>
+      <c r="C195">
+        <v>20.8063175394846</v>
+      </c>
+    </row>
+    <row r="196">
+      <c r="A196" t="inlineStr">
+        <is>
+          <t>10306</t>
+        </is>
+      </c>
+      <c r="B196" t="inlineStr">
+        <is>
+          <t>San Juan de la Costa</t>
+        </is>
+      </c>
+      <c r="C196">
+        <v>19.5511982570806</v>
+      </c>
+    </row>
+    <row r="197">
+      <c r="A197" t="inlineStr">
+        <is>
+          <t>10306</t>
+        </is>
+      </c>
+      <c r="B197" t="inlineStr">
+        <is>
+          <t>San Juan de la Costa</t>
+        </is>
+      </c>
+      <c r="C197">
         <v>17.3561316418459</v>
+      </c>
+    </row>
+    <row r="198">
+      <c r="A198" t="inlineStr">
+        <is>
+          <t>10103</t>
+        </is>
+      </c>
+      <c r="B198" t="inlineStr">
+        <is>
+          <t>Cochamó</t>
+        </is>
+      </c>
+      <c r="C198">
+        <v>17.1432537479178</v>
+      </c>
+    </row>
+    <row r="199">
+      <c r="A199" t="inlineStr">
+        <is>
+          <t>10306</t>
+        </is>
+      </c>
+      <c r="B199" t="inlineStr">
+        <is>
+          <t>San Juan de la Costa</t>
+        </is>
+      </c>
+      <c r="C199">
+        <v>14.9061375352592</v>
+      </c>
+    </row>
+    <row r="200">
+      <c r="A200" t="inlineStr">
+        <is>
+          <t>10109</t>
+        </is>
+      </c>
+      <c r="B200" t="inlineStr">
+        <is>
+          <t>Puerto Varas</t>
+        </is>
+      </c>
+      <c r="C200">
+        <v>14.1591532084943</v>
+      </c>
+    </row>
+    <row r="201">
+      <c r="A201" t="inlineStr">
+        <is>
+          <t>10101</t>
+        </is>
+      </c>
+      <c r="B201" t="inlineStr">
+        <is>
+          <t>Puerto Montt</t>
+        </is>
+      </c>
+      <c r="C201">
+        <v>12.7382023076509</v>
+      </c>
+    </row>
+    <row r="202">
+      <c r="A202" t="inlineStr">
+        <is>
+          <t>10107</t>
+        </is>
+      </c>
+      <c r="B202" t="inlineStr">
+        <is>
+          <t>Llanquihue</t>
+        </is>
+      </c>
+      <c r="C202">
+        <v>12.7284183994959</v>
+      </c>
+    </row>
+    <row r="203">
+      <c r="A203" t="inlineStr">
+        <is>
+          <t>10302</t>
+        </is>
+      </c>
+      <c r="B203" t="inlineStr">
+        <is>
+          <t>Puerto Octay</t>
+        </is>
+      </c>
+      <c r="C203">
+        <v>12.2043730477465</v>
+      </c>
+    </row>
+    <row r="204">
+      <c r="A204" t="inlineStr">
+        <is>
+          <t>10105</t>
+        </is>
+      </c>
+      <c r="B204" t="inlineStr">
+        <is>
+          <t>Frutillar</t>
+        </is>
+      </c>
+      <c r="C204">
+        <v>11.9823015190599</v>
+      </c>
+    </row>
+    <row r="205">
+      <c r="A205" t="inlineStr">
+        <is>
+          <t>10107</t>
+        </is>
+      </c>
+      <c r="B205" t="inlineStr">
+        <is>
+          <t>Llanquihue</t>
+        </is>
+      </c>
+      <c r="C205">
+        <v>11.4338587719612</v>
+      </c>
+    </row>
+    <row r="206">
+      <c r="A206" t="inlineStr">
+        <is>
+          <t>10304</t>
+        </is>
+      </c>
+      <c r="B206" t="inlineStr">
+        <is>
+          <t>Puyehue</t>
+        </is>
+      </c>
+      <c r="C206">
+        <v>11.120178041543</v>
+      </c>
+    </row>
+    <row r="207">
+      <c r="A207" t="inlineStr">
+        <is>
+          <t>10208</t>
+        </is>
+      </c>
+      <c r="B207" t="inlineStr">
+        <is>
+          <t>Quellón</t>
+        </is>
+      </c>
+      <c r="C207">
+        <v>10.7491619297478</v>
+      </c>
+    </row>
+    <row r="208">
+      <c r="A208" t="inlineStr">
+        <is>
+          <t>10305</t>
+        </is>
+      </c>
+      <c r="B208" t="inlineStr">
+        <is>
+          <t>Río Negro</t>
+        </is>
+      </c>
+      <c r="C208">
+        <v>10.6137797185832</v>
+      </c>
+    </row>
+    <row r="209">
+      <c r="A209" t="inlineStr">
+        <is>
+          <t>10301</t>
+        </is>
+      </c>
+      <c r="B209" t="inlineStr">
+        <is>
+          <t>Osorno</t>
+        </is>
+      </c>
+      <c r="C209">
+        <v>10.5665203656593</v>
+      </c>
+    </row>
+    <row r="210">
+      <c r="A210" t="inlineStr">
+        <is>
+          <t>10307</t>
+        </is>
+      </c>
+      <c r="B210" t="inlineStr">
+        <is>
+          <t>San Pablo</t>
+        </is>
+      </c>
+      <c r="C210">
+        <v>10.2524787897373</v>
+      </c>
+    </row>
+    <row r="211">
+      <c r="A211" t="inlineStr">
+        <is>
+          <t>10301</t>
+        </is>
+      </c>
+      <c r="B211" t="inlineStr">
+        <is>
+          <t>Osorno</t>
+        </is>
+      </c>
+      <c r="C211">
+        <v>10.2408500032483</v>
+      </c>
+    </row>
+    <row r="212">
+      <c r="A212" t="inlineStr">
+        <is>
+          <t>10401</t>
+        </is>
+      </c>
+      <c r="B212" t="inlineStr">
+        <is>
+          <t>Chaitén</t>
+        </is>
+      </c>
+      <c r="C212">
+        <v>10.1764335223692</v>
+      </c>
+    </row>
+    <row r="213">
+      <c r="A213" t="inlineStr">
+        <is>
+          <t>10201</t>
+        </is>
+      </c>
+      <c r="B213" t="inlineStr">
+        <is>
+          <t>Castro</t>
+        </is>
+      </c>
+      <c r="C213">
+        <v>9.756899985773231</v>
+      </c>
+    </row>
+    <row r="214">
+      <c r="A214" t="inlineStr">
+        <is>
+          <t>10303</t>
+        </is>
+      </c>
+      <c r="B214" t="inlineStr">
+        <is>
+          <t>Purranque</t>
+        </is>
+      </c>
+      <c r="C214">
+        <v>9.486866027208331</v>
+      </c>
+    </row>
+    <row r="215">
+      <c r="A215" t="inlineStr">
+        <is>
+          <t>10202</t>
+        </is>
+      </c>
+      <c r="B215" t="inlineStr">
+        <is>
+          <t>Ancud</t>
+        </is>
+      </c>
+      <c r="C215">
+        <v>9.19972098037351</v>
+      </c>
+    </row>
+    <row r="216">
+      <c r="A216" t="inlineStr">
+        <is>
+          <t>10403</t>
+        </is>
+      </c>
+      <c r="B216" t="inlineStr">
+        <is>
+          <t>Hualaihué</t>
+        </is>
+      </c>
+      <c r="C216">
+        <v>8.8409475465313</v>
+      </c>
+    </row>
+    <row r="217">
+      <c r="A217" t="inlineStr">
+        <is>
+          <t>10404</t>
+        </is>
+      </c>
+      <c r="B217" t="inlineStr">
+        <is>
+          <t>Palena</t>
+        </is>
+      </c>
+      <c r="C217">
+        <v>8.43832020997375</v>
+      </c>
+    </row>
+    <row r="218">
+      <c r="A218" t="inlineStr">
+        <is>
+          <t>10204</t>
+        </is>
+      </c>
+      <c r="B218" t="inlineStr">
+        <is>
+          <t>Curaco de Vélez</t>
+        </is>
+      </c>
+      <c r="C218">
+        <v>8.23539886039886</v>
+      </c>
+    </row>
+    <row r="219">
+      <c r="A219" t="inlineStr">
+        <is>
+          <t>10203</t>
+        </is>
+      </c>
+      <c r="B219" t="inlineStr">
+        <is>
+          <t>Chonchi</t>
+        </is>
+      </c>
+      <c r="C219">
+        <v>8.1225236208473</v>
+      </c>
+    </row>
+    <row r="220">
+      <c r="A220" t="inlineStr">
+        <is>
+          <t>10205</t>
+        </is>
+      </c>
+      <c r="B220" t="inlineStr">
+        <is>
+          <t>Dalcahue</t>
+        </is>
+      </c>
+      <c r="C220">
+        <v>7.82587228439763</v>
+      </c>
+    </row>
+    <row r="221">
+      <c r="A221" t="inlineStr">
+        <is>
+          <t>10102</t>
+        </is>
+      </c>
+      <c r="B221" t="inlineStr">
+        <is>
+          <t>Calbuco</t>
+        </is>
+      </c>
+      <c r="C221">
+        <v>7.80798447692181</v>
+      </c>
+    </row>
+    <row r="222">
+      <c r="A222" t="inlineStr">
+        <is>
+          <t>10104</t>
+        </is>
+      </c>
+      <c r="B222" t="inlineStr">
+        <is>
+          <t>Fresia</t>
+        </is>
+      </c>
+      <c r="C222">
+        <v>7.54027077774484</v>
+      </c>
+    </row>
+    <row r="223">
+      <c r="A223" t="inlineStr">
+        <is>
+          <t>10210</t>
+        </is>
+      </c>
+      <c r="B223" t="inlineStr">
+        <is>
+          <t>Quinchao</t>
+        </is>
+      </c>
+      <c r="C223">
+        <v>7.45132301547678</v>
+      </c>
+    </row>
+    <row r="224">
+      <c r="A224" t="inlineStr">
+        <is>
+          <t>10404</t>
+        </is>
+      </c>
+      <c r="B224" t="inlineStr">
+        <is>
+          <t>Palena</t>
+        </is>
+      </c>
+      <c r="C224">
+        <v>7.32323232323232</v>
+      </c>
+    </row>
+    <row r="225">
+      <c r="A225" t="inlineStr">
+        <is>
+          <t>10207</t>
+        </is>
+      </c>
+      <c r="B225" t="inlineStr">
+        <is>
+          <t>Queilén</t>
+        </is>
+      </c>
+      <c r="C225">
+        <v>7.26415094339623</v>
+      </c>
+    </row>
+    <row r="226">
+      <c r="A226" t="inlineStr">
+        <is>
+          <t>10108</t>
+        </is>
+      </c>
+      <c r="B226" t="inlineStr">
+        <is>
+          <t>Maullín</t>
+        </is>
+      </c>
+      <c r="C226">
+        <v>7.04016252539459</v>
+      </c>
+    </row>
+    <row r="227">
+      <c r="A227" t="inlineStr">
+        <is>
+          <t>10106</t>
+        </is>
+      </c>
+      <c r="B227" t="inlineStr">
+        <is>
+          <t>Los Muermos</t>
+        </is>
+      </c>
+      <c r="C227">
+        <v>6.11747010052095</v>
+      </c>
+    </row>
+    <row r="228">
+      <c r="A228" t="inlineStr">
+        <is>
+          <t>10209</t>
+        </is>
+      </c>
+      <c r="B228" t="inlineStr">
+        <is>
+          <t>Quemchi</t>
+        </is>
+      </c>
+      <c r="C228">
+        <v>5.84351893767919</v>
+      </c>
+    </row>
+    <row r="229">
+      <c r="A229" t="inlineStr">
+        <is>
+          <t>10103</t>
+        </is>
+      </c>
+      <c r="B229" t="inlineStr">
+        <is>
+          <t>Cochamó</t>
+        </is>
+      </c>
+      <c r="C229">
+        <v>5.8064070698702</v>
+      </c>
+    </row>
+    <row r="230">
+      <c r="A230" t="inlineStr">
+        <is>
+          <t>10402</t>
+        </is>
+      </c>
+      <c r="B230" t="inlineStr">
+        <is>
+          <t>Futaleufú</t>
+        </is>
+      </c>
+      <c r="C230">
+        <v>5.27314112291351</v>
+      </c>
+    </row>
+    <row r="231">
+      <c r="A231" t="inlineStr">
+        <is>
+          <t>10206</t>
+        </is>
+      </c>
+      <c r="B231" t="inlineStr">
+        <is>
+          <t>Puqueldón</t>
+        </is>
+      </c>
+      <c r="C231">
+        <v>4.85770363101079</v>
+      </c>
+    </row>
+    <row r="232">
+      <c r="A232" t="inlineStr">
+        <is>
+          <t>10306</t>
+        </is>
+      </c>
+      <c r="B232" t="inlineStr">
+        <is>
+          <t>San Juan de la Costa</t>
+        </is>
+      </c>
+      <c r="C232">
+        <v>3.20676000565691</v>
       </c>
     </row>
   </sheetData>
